--- a/public/exel/Form1.xlsx
+++ b/public/exel/Form1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sbfp_ao_system\public\exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCC9842-ADF9-4CFD-88B8-472B35ED2998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6F0043-5DAE-42D3-9F8B-7111874BB942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,7 +396,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -465,11 +465,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1251,7 +1246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1361,41 +1356,14 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1403,6 +1371,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1412,6 +1381,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1419,6 +1391,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1438,14 +1437,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1458,12 +1457,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1525,9 +1518,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
+      <xdr:colOff>607869</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>170007</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="742950" cy="409575"/>
     <xdr:pic>
@@ -1551,8 +1544,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="15374505" y="331643"/>
+          <a:ext cx="742950" cy="409575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1819,230 +1812,233 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
+      <c r="B1" s="74"/>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
-      <c r="O2" s="69"/>
-      <c r="P2" s="69"/>
-      <c r="Q2" s="69"/>
-      <c r="R2" s="69"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="75"/>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75"/>
     </row>
     <row r="3" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
-      <c r="M3" s="70"/>
-      <c r="N3" s="70"/>
-      <c r="O3" s="70"/>
-      <c r="P3" s="70"/>
-      <c r="Q3" s="70"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="70"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
     </row>
     <row r="4" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="72"/>
-      <c r="Q4" s="72"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="72"/>
-      <c r="T4" s="72"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
+      <c r="N4" s="77"/>
+      <c r="O4" s="77"/>
+      <c r="P4" s="77"/>
+      <c r="Q4" s="77"/>
+      <c r="R4" s="77"/>
+      <c r="S4" s="77"/>
+      <c r="T4" s="77"/>
+      <c r="U4" s="77"/>
     </row>
     <row r="5" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="73"/>
-      <c r="C6" s="73"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="73"/>
-      <c r="F6" s="73"/>
-      <c r="H6" s="74" t="s">
+      <c r="B6" s="66"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="66"/>
+      <c r="E6" s="66"/>
+      <c r="F6" s="66"/>
+      <c r="H6" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="74"/>
-      <c r="J6" s="74"/>
-      <c r="K6" s="74"/>
-      <c r="L6" s="74"/>
-      <c r="M6" s="74"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
     </row>
     <row r="7" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="66" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="H7" s="74" t="s">
+      <c r="B7" s="66"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="H7" s="70" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="74"/>
-      <c r="M7" s="74"/>
+      <c r="I7" s="70"/>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="70"/>
+      <c r="M7" s="70"/>
     </row>
     <row r="8" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="73" t="s">
+      <c r="A8" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="73"/>
-      <c r="C8" s="73"/>
-      <c r="D8" s="73"/>
-      <c r="E8" s="73"/>
-      <c r="F8" s="73"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="66"/>
+      <c r="F8" s="66"/>
     </row>
     <row r="9" spans="1:21" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="73" t="s">
+      <c r="A9" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
+      <c r="B9" s="66"/>
+      <c r="C9" s="66"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="66"/>
+      <c r="F9" s="66"/>
     </row>
     <row r="10" spans="1:21" ht="3.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:21" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="80" t="s">
+      <c r="A11" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="82" t="s">
+      <c r="B11" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="75" t="s">
+      <c r="D11" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="75" t="s">
+      <c r="E11" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="79" t="s">
+      <c r="F11" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="75" t="s">
+      <c r="G11" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="75" t="s">
+      <c r="H11" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="75"/>
-      <c r="J11" s="75" t="s">
+      <c r="I11" s="64"/>
+      <c r="J11" s="64" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="75" t="s">
+      <c r="K11" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="75" t="s">
+      <c r="L11" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="75" t="s">
+      <c r="M11" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="76"/>
-      <c r="O11" s="62" t="s">
+      <c r="N11" s="65"/>
+      <c r="O11" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="P11" s="62" t="s">
+      <c r="P11" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="Q11" s="62" t="s">
+      <c r="Q11" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="R11" s="62" t="s">
+      <c r="R11" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="S11" s="62" t="s">
+      <c r="S11" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="T11" s="65" t="s">
+      <c r="T11" s="81" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="104" t="s">
+      <c r="U11" s="62" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="81"/>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="68"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
       <c r="H12" s="58" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="77"/>
-      <c r="K12" s="77"/>
-      <c r="L12" s="77"/>
+      <c r="J12" s="67"/>
+      <c r="K12" s="67"/>
+      <c r="L12" s="67"/>
       <c r="M12" s="59" t="s">
         <v>29</v>
       </c>
       <c r="N12" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="O12" s="64"/>
-      <c r="P12" s="64"/>
-      <c r="Q12" s="63"/>
-      <c r="R12" s="63"/>
-      <c r="S12" s="64"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="105"/>
+      <c r="O12" s="80"/>
+      <c r="P12" s="80"/>
+      <c r="Q12" s="79"/>
+      <c r="R12" s="79"/>
+      <c r="S12" s="80"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="63"/>
     </row>
     <row r="13" spans="1:21" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="49"/>
@@ -46774,6 +46770,19 @@
     <row r="2047" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:M6"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
     <mergeCell ref="U11:U12"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="A7:F7"/>
@@ -46790,19 +46799,6 @@
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:T2"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="A4:T4"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:M6"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="P11:P12"/>
   </mergeCells>
   <pageMargins left="0.11811023622047" right="3.9370078740157001E-2" top="0.11811023622047" bottom="0.11811023622047" header="0.11811023622047" footer="0.11811023622047"/>
   <pageSetup paperSize="14" scale="70" orientation="landscape" r:id="rId1"/>
@@ -46834,7 +46830,7 @@
     </row>
     <row r="2" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="75" t="s">
         <v>33</v>
       </c>
       <c r="B3" s="83"/>
@@ -46857,7 +46853,7 @@
     </row>
     <row r="4" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="77" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="83"/>
@@ -46879,7 +46875,7 @@
       <c r="R5" s="83"/>
     </row>
     <row r="6" spans="1:18" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
+      <c r="A6" s="75"/>
       <c r="B6" s="83"/>
       <c r="C6" s="83"/>
       <c r="D6" s="83"/>
@@ -47611,7 +47607,7 @@
       <c r="D43" s="41"/>
       <c r="E43" s="41"/>
       <c r="F43" s="41"/>
-      <c r="H43" s="70" t="s">
+      <c r="H43" s="76" t="s">
         <v>68</v>
       </c>
       <c r="I43" s="83"/>
@@ -47626,7 +47622,7 @@
         <v>69</v>
       </c>
       <c r="C44" s="1"/>
-      <c r="H44" s="70" t="s">
+      <c r="H44" s="76" t="s">
         <v>31</v>
       </c>
       <c r="I44" s="83"/>
